--- a/backend/data/financials_by_company/002361.SZ.xlsx
+++ b/backend/data/financials_by_company/002361.SZ.xlsx
@@ -4165,10 +4165,8 @@
           <t>Wuhu</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>241008</t>
-        </is>
+      <c r="D2" t="n">
+        <v>241008</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4391,7 +4389,7 @@
         <v>-3837181</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -4644,7 +4642,7 @@
         <v>1619780340</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
